--- a/static/example_sheets/eDNA Wet lab final report.xlsx
+++ b/static/example_sheets/eDNA Wet lab final report.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27321"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\working\waccache\GVX0EPF00012A7E\EXCELCNV\4cc871f1-f842-4fc2-94ee-b94eca113837\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\glj523\Documents\github repoes\upload_web_app\static\example_sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{708B8007-07A3-45BE-B7BE-846C98985D01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{209B5D6F-5251-4CB7-BB1B-9FB08F1ECD69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="15480" windowHeight="11640" tabRatio="150" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" tabRatio="150" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Copy Of Progress sheet_Sediment" sheetId="1" r:id="rId1"/>
@@ -729,7 +729,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -1200,47 +1200,46 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AU22"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" customWidth="1"/>
+    <col min="1" max="1" width="17.6640625" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="6.28515625" customWidth="1"/>
+    <col min="4" max="4" width="6.33203125" customWidth="1"/>
     <col min="5" max="5" width="7" customWidth="1"/>
-    <col min="6" max="6" width="24.140625" customWidth="1"/>
+    <col min="6" max="6" width="24.109375" customWidth="1"/>
     <col min="7" max="7" width="19" customWidth="1"/>
-    <col min="8" max="8" width="8.140625" customWidth="1"/>
-    <col min="9" max="9" width="19.140625" customWidth="1"/>
-    <col min="10" max="10" width="20.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.85546875" customWidth="1"/>
-    <col min="12" max="12" width="7.42578125" customWidth="1"/>
-    <col min="13" max="13" width="12.28515625" customWidth="1"/>
-    <col min="14" max="14" width="15.85546875" customWidth="1"/>
-    <col min="15" max="15" width="6.28515625" customWidth="1"/>
-    <col min="16" max="16" width="0.28515625" customWidth="1"/>
-    <col min="17" max="17" width="14.140625" customWidth="1"/>
-    <col min="18" max="18" width="13.85546875" customWidth="1"/>
-    <col min="19" max="19" width="73.42578125" customWidth="1"/>
+    <col min="8" max="8" width="8.109375" customWidth="1"/>
+    <col min="9" max="9" width="19.109375" customWidth="1"/>
+    <col min="10" max="10" width="20.6640625" customWidth="1"/>
+    <col min="11" max="11" width="21.88671875" customWidth="1"/>
+    <col min="12" max="12" width="7.44140625" customWidth="1"/>
+    <col min="13" max="13" width="12.33203125" customWidth="1"/>
+    <col min="14" max="14" width="15.88671875" customWidth="1"/>
+    <col min="15" max="15" width="6.33203125" customWidth="1"/>
+    <col min="16" max="17" width="15.88671875" customWidth="1"/>
+    <col min="18" max="18" width="13.88671875" customWidth="1"/>
+    <col min="19" max="19" width="73.44140625" customWidth="1"/>
     <col min="20" max="20" width="18" customWidth="1"/>
-    <col min="21" max="21" width="21.28515625" customWidth="1"/>
-    <col min="22" max="22" width="7.140625" customWidth="1"/>
+    <col min="21" max="21" width="21.33203125" customWidth="1"/>
+    <col min="22" max="22" width="7.109375" customWidth="1"/>
     <col min="23" max="23" width="14" customWidth="1"/>
-    <col min="24" max="24" width="8.5703125" customWidth="1"/>
-    <col min="25" max="25" width="13.85546875" customWidth="1"/>
-    <col min="26" max="26" width="8.5703125" customWidth="1"/>
-    <col min="27" max="30" width="13.85546875" customWidth="1"/>
+    <col min="24" max="24" width="8.5546875" customWidth="1"/>
+    <col min="25" max="25" width="13.88671875" customWidth="1"/>
+    <col min="26" max="26" width="8.5546875" customWidth="1"/>
+    <col min="27" max="30" width="13.88671875" customWidth="1"/>
     <col min="31" max="31" width="13" customWidth="1"/>
-    <col min="32" max="33" width="13.85546875" customWidth="1"/>
-    <col min="34" max="34" width="6.85546875" customWidth="1"/>
-    <col min="35" max="37" width="13.85546875" customWidth="1"/>
-    <col min="38" max="38" width="48.5703125" customWidth="1"/>
-    <col min="39" max="39" width="15.28515625" customWidth="1"/>
+    <col min="32" max="33" width="13.88671875" customWidth="1"/>
+    <col min="34" max="34" width="6.88671875" customWidth="1"/>
+    <col min="35" max="37" width="13.88671875" customWidth="1"/>
+    <col min="38" max="38" width="48.5546875" customWidth="1"/>
+    <col min="39" max="39" width="15.33203125" customWidth="1"/>
     <col min="40" max="40" width="20" customWidth="1"/>
-    <col min="41" max="46" width="13.85546875" customWidth="1"/>
-    <col min="47" max="47" width="19.42578125" customWidth="1"/>
+    <col min="41" max="46" width="13.88671875" customWidth="1"/>
+    <col min="47" max="47" width="19.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" ht="14.45" customHeight="1">
+    <row r="1" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1383,7 +1382,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:47" ht="14.45" customHeight="1">
+    <row r="2" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>47</v>
       </c>
@@ -1523,7 +1522,7 @@
         <v>45300</v>
       </c>
     </row>
-    <row r="3" spans="1:47" ht="14.45" customHeight="1">
+    <row r="3" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>47</v>
       </c>
@@ -1663,7 +1662,7 @@
         <v>45300</v>
       </c>
     </row>
-    <row r="4" spans="1:47" ht="14.45" customHeight="1">
+    <row r="4" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>47</v>
       </c>
@@ -1803,7 +1802,7 @@
         <v>45300</v>
       </c>
     </row>
-    <row r="5" spans="1:47" ht="14.45" customHeight="1">
+    <row r="5" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>47</v>
       </c>
@@ -1943,7 +1942,7 @@
         <v>45300</v>
       </c>
     </row>
-    <row r="6" spans="1:47" ht="14.45" customHeight="1">
+    <row r="6" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>47</v>
       </c>
@@ -2083,7 +2082,7 @@
         <v>45300</v>
       </c>
     </row>
-    <row r="7" spans="1:47" ht="14.45" customHeight="1">
+    <row r="7" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>47</v>
       </c>
@@ -2223,7 +2222,7 @@
         <v>45300</v>
       </c>
     </row>
-    <row r="8" spans="1:47" ht="14.45" customHeight="1">
+    <row r="8" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>47</v>
       </c>
@@ -2363,7 +2362,7 @@
         <v>45300</v>
       </c>
     </row>
-    <row r="9" spans="1:47" ht="14.45" customHeight="1">
+    <row r="9" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>47</v>
       </c>
@@ -2503,7 +2502,7 @@
         <v>45300</v>
       </c>
     </row>
-    <row r="10" spans="1:47" ht="14.45" customHeight="1">
+    <row r="10" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>47</v>
       </c>
@@ -2643,7 +2642,7 @@
         <v>45300</v>
       </c>
     </row>
-    <row r="11" spans="1:47" ht="14.45" customHeight="1">
+    <row r="11" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>47</v>
       </c>
@@ -2783,7 +2782,7 @@
         <v>45300</v>
       </c>
     </row>
-    <row r="12" spans="1:47" ht="14.45" customHeight="1">
+    <row r="12" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>47</v>
       </c>
@@ -2923,7 +2922,7 @@
         <v>45300</v>
       </c>
     </row>
-    <row r="13" spans="1:47" ht="14.45" customHeight="1">
+    <row r="13" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>47</v>
       </c>
@@ -3063,7 +3062,7 @@
         <v>45300</v>
       </c>
     </row>
-    <row r="14" spans="1:47" ht="14.45" customHeight="1">
+    <row r="14" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>47</v>
       </c>
@@ -3203,7 +3202,7 @@
         <v>45300</v>
       </c>
     </row>
-    <row r="15" spans="1:47" ht="14.45" customHeight="1">
+    <row r="15" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>47</v>
       </c>
@@ -3343,7 +3342,7 @@
         <v>45300</v>
       </c>
     </row>
-    <row r="16" spans="1:47" ht="14.45" customHeight="1">
+    <row r="16" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>47</v>
       </c>
@@ -3483,7 +3482,7 @@
         <v>45300</v>
       </c>
     </row>
-    <row r="17" spans="1:47" ht="14.45" customHeight="1">
+    <row r="17" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>47</v>
       </c>
@@ -3623,7 +3622,7 @@
         <v>45300</v>
       </c>
     </row>
-    <row r="18" spans="1:47" ht="14.45" customHeight="1">
+    <row r="18" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>47</v>
       </c>
@@ -3763,7 +3762,7 @@
         <v>45300</v>
       </c>
     </row>
-    <row r="19" spans="1:47" ht="14.45" customHeight="1">
+    <row r="19" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>47</v>
       </c>
@@ -3903,7 +3902,7 @@
         <v>45300</v>
       </c>
     </row>
-    <row r="20" spans="1:47" ht="14.45" customHeight="1">
+    <row r="20" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>47</v>
       </c>
@@ -4043,7 +4042,7 @@
         <v>45300</v>
       </c>
     </row>
-    <row r="21" spans="1:47" ht="14.45" customHeight="1">
+    <row r="21" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>47</v>
       </c>
@@ -4183,7 +4182,7 @@
         <v>45300</v>
       </c>
     </row>
-    <row r="22" spans="1:47" ht="14.45" customHeight="1">
+    <row r="22" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>47</v>
       </c>
@@ -4329,15 +4328,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010015BC63EE602A9B4B90EAFA524706E7EC" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e3ae851e25a0dfe4f43afaeb30e48fad">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="344093a9-d904-4ffb-8b7b-de0b820fd76b" xmlns:ns3="5795b8a2-0df7-4793-b5f3-596dc329b202" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="245f29a22b45e42c32918cc1d62f0ec2" ns2:_="" ns3:_="">
     <xsd:import namespace="344093a9-d904-4ffb-8b7b-de0b820fd76b"/>
@@ -4590,10 +4580,38 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E26BC993-C9ED-4A02-981D-F040524728A6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB936197-5F8A-417F-AE64-33E4A0726662}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="344093a9-d904-4ffb-8b7b-de0b820fd76b"/>
+    <ds:schemaRef ds:uri="5795b8a2-0df7-4793-b5f3-596dc329b202"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB936197-5F8A-417F-AE64-33E4A0726662}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E26BC993-C9ED-4A02-981D-F040524728A6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>